--- a/data/trans_bre/P2A_ner_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P2A_ner_R-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 6,85</t>
+          <t>-0,81; 7,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 6,61</t>
+          <t>-0,73; 6,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,19; 14,38</t>
+          <t>3,65; 14,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 0,99</t>
+          <t>-4,33; 1,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-21,67; 339,03</t>
+          <t>-22,8; 392,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-21,01; 307,04</t>
+          <t>-18,81; 272,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,44; 280,75</t>
+          <t>34,73; 276,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-72,95; 52,52</t>
+          <t>-75,36; 60,93</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 4,47</t>
+          <t>-0,6; 4,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 5,67</t>
+          <t>0,38; 5,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,87; 10,19</t>
+          <t>3,85; 10,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 5,75</t>
+          <t>1,39; 5,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-22,23; 174,51</t>
+          <t>-13,3; 172,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 298,8</t>
+          <t>5,38; 340,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>80,86; 463,8</t>
+          <t>84,83; 498,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>23,3; 390,94</t>
+          <t>31,59; 398,43</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 1,95</t>
+          <t>-0,6; 1,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 1,49</t>
+          <t>-2,73; 1,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,24; 11,27</t>
+          <t>3,74; 10,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 4,15</t>
+          <t>-1,73; 4,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,17 +885,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-76,73; 129,91</t>
+          <t>-75,7; 163,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>109,9; 1401,47</t>
+          <t>89,19; 1124,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-38,67; 191,4</t>
+          <t>-32,2; 198,53</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 4,82</t>
+          <t>-0,18; 4,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,28; 9,26</t>
+          <t>3,13; 9,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,14; 7,59</t>
+          <t>0,29; 7,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 0,92</t>
+          <t>-6,68; 0,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,03; 453,06</t>
+          <t>-19,63; 486,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,8; 677,01</t>
+          <t>64,58; 591,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 249,87</t>
+          <t>2,95; 228,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-73,52; 24,46</t>
+          <t>-74,07; 33,99</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 7,7</t>
+          <t>-0,85; 7,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 10,73</t>
+          <t>-1,32; 10,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,52; 12,15</t>
+          <t>0,79; 12,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 2,86</t>
+          <t>-0,82; 3,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-31,07; 280,95</t>
+          <t>-23,33; 340,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-19,86; 162,96</t>
+          <t>-12,03; 172,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,61; 235,38</t>
+          <t>-1,39; 226,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-46,87; 741,08</t>
+          <t>-42,59; 982,41</t>
         </is>
       </c>
     </row>
@@ -1160,27 +1160,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 5,01</t>
+          <t>-0,3; 5,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,15; 5,74</t>
+          <t>1,18; 6,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,33; 12,78</t>
+          <t>3,64; 12,86</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 2,48</t>
+          <t>-2,67; 2,48</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-41,86; 816,21</t>
+          <t>-28,36; 1094,73</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1190,12 +1190,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>52,43; 464,47</t>
+          <t>54,45; 491,29</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-53,6; 108,43</t>
+          <t>-50,1; 99,1</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,11; 3,66</t>
+          <t>0,1; 3,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 1,22</t>
+          <t>-2,19; 1,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,03; 10,0</t>
+          <t>4,02; 10,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,45; 55,37</t>
+          <t>0,65; 60,09</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 317,96</t>
+          <t>-0,59; 323,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-61,48; 66,02</t>
+          <t>-61,07; 75,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,41; 346,47</t>
+          <t>71,45; 347,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,62; 1894,86</t>
+          <t>13,33; 1545,55</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 3,84</t>
+          <t>-0,83; 3,56</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 2,37</t>
+          <t>-1,31; 2,4</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,38; 8,85</t>
+          <t>3,03; 8,77</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,99; 4,37</t>
+          <t>0,84; 4,1</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-16,45; 111,06</t>
+          <t>-15,7; 107,01</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-34,85; 109,31</t>
+          <t>-33,52; 126,35</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>54,68; 245,29</t>
+          <t>48,13; 237,18</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>33,16; 480,0</t>
+          <t>32,01; 440,86</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,71</t>
+          <t>0,97; 2,8</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,93</t>
+          <t>0,9; 2,81</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,18; 7,74</t>
+          <t>5,24; 7,83</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,88; 23,61</t>
+          <t>0,93; 23,54</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>24,12; 112,13</t>
+          <t>29,09; 114,4</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26,38; 109,49</t>
+          <t>25,21; 106,76</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>102,14; 197,09</t>
+          <t>104,1; 194,76</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>24,67; 863,0</t>
+          <t>25,51; 828,48</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_ner_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P2A_ner_R-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,26</t>
+          <t>-0,68</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-34,65%</t>
+          <t>-21,28%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 7,07</t>
+          <t>-0,82; 6,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 6,31</t>
+          <t>-0,01; 7,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,65; 14,58</t>
+          <t>3,37; 14,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 1,07</t>
+          <t>-3,42; 1,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-22,8; 392,9</t>
+          <t>-27,51; 295,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-18,81; 272,42</t>
+          <t>-5,68; 355,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,73; 276,08</t>
+          <t>34,49; 279,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-75,36; 60,93</t>
+          <t>-65,78; 79,33</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,52</t>
+          <t>3,38</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>142,51%</t>
+          <t>135,92%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 4,28</t>
+          <t>-0,75; 4,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,38; 5,92</t>
+          <t>0,01; 5,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,85; 10,2</t>
+          <t>3,67; 10,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,39; 5,9</t>
+          <t>1,39; 5,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-13,3; 172,93</t>
+          <t>-18,48; 174,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,38; 340,3</t>
+          <t>-7,83; 325,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84,83; 498,66</t>
+          <t>76,45; 437,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>31,59; 398,43</t>
+          <t>31,88; 365,76</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,62</t>
+          <t>1,8</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>53,84%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 1,75</t>
+          <t>-0,61; 1,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 1,67</t>
+          <t>-2,73; 1,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,74; 10,68</t>
+          <t>3,96; 11,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 4,34</t>
+          <t>-1,77; 4,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,17 +885,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-75,7; 163,11</t>
+          <t>-80,56; 132,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>89,19; 1124,53</t>
+          <t>104,17; 1219,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-32,2; 198,53</t>
+          <t>-31,78; 217,12</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,18</t>
+          <t>-0,88</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-38,08%</t>
+          <t>-16,77%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 4,84</t>
+          <t>-0,34; 4,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,13; 9,41</t>
+          <t>3,3; 9,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 7,4</t>
+          <t>0,21; 7,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 0,96</t>
+          <t>-4,75; 2,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-19,63; 486,09</t>
+          <t>-21,84; 467,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,58; 591,42</t>
+          <t>78,91; 661,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,95; 228,12</t>
+          <t>-1,5; 223,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-74,07; 33,99</t>
+          <t>-62,56; 71,2</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,23</t>
+          <t>1,79</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>107,49%</t>
+          <t>165,67%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 7,81</t>
+          <t>-1,25; 8,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 10,71</t>
+          <t>-1,81; 10,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,79; 12,56</t>
+          <t>0,82; 12,76</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 3,12</t>
+          <t>-0,11; 3,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-23,33; 340,6</t>
+          <t>-28,27; 369,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,03; 172,53</t>
+          <t>-15,1; 158,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 226,51</t>
+          <t>2,63; 250,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-42,59; 982,41</t>
+          <t>-26,69; 1213,72</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0,04</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-0,91%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -1160,27 +1160,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 5,15</t>
+          <t>-0,35; 4,98</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,18; 6,06</t>
+          <t>1,38; 6,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,64; 12,86</t>
+          <t>2,95; 13,03</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 2,48</t>
+          <t>-2,86; 2,47</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-28,36; 1094,73</t>
+          <t>-36,49; 921,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1190,12 +1190,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>54,45; 491,29</t>
+          <t>36,01; 464,71</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-50,1; 99,1</t>
+          <t>-50,92; 99,65</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23,91</t>
+          <t>1,59</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>483,7%</t>
+          <t>31,06%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 3,44</t>
+          <t>0,05; 3,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 1,19</t>
+          <t>-2,28; 1,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,02; 10,27</t>
+          <t>3,96; 9,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,65; 60,09</t>
+          <t>-1,07; 3,93</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 323,37</t>
+          <t>-3,39; 299,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-61,07; 75,26</t>
+          <t>-62,09; 71,36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,45; 347,74</t>
+          <t>65,8; 315,7</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13,33; 1545,55</t>
+          <t>-16,64; 101,71</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2,41</t>
+          <t>1,71</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>136,74%</t>
+          <t>70,19%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 3,56</t>
+          <t>-0,98; 3,74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 2,4</t>
+          <t>-1,46; 2,28</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,03; 8,77</t>
+          <t>3,5; 8,65</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,84; 4,1</t>
+          <t>0,29; 3,37</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-15,7; 107,01</t>
+          <t>-18,65; 117,54</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-33,52; 126,35</t>
+          <t>-36,46; 101,98</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,13; 237,18</t>
+          <t>59,72; 235,65</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>32,01; 440,86</t>
+          <t>6,99; 209,91</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6,53</t>
+          <t>1,35</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>199,66%</t>
+          <t>39,07%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,8</t>
+          <t>0,94; 2,79</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,81</t>
+          <t>0,95; 2,86</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,24; 7,83</t>
+          <t>5,11; 7,78</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,93; 23,54</t>
+          <t>0,45; 2,31</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>29,09; 114,4</t>
+          <t>28,71; 116,58</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,21; 106,76</t>
+          <t>26,41; 108,82</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>104,1; 194,76</t>
+          <t>101,07; 195,68</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>25,51; 828,48</t>
+          <t>11,1; 79,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_ner_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P2A_ner_R-Provincia-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental</t>
+          <t>Población que convive con personas con problemas de nervios, depresión o trastorno mental</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
